--- a/AAII_Financials/Quarterly/ILUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ILUS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>ILUS</t>
   </si>
@@ -656,173 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E8" s="3">
         <v>23500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2900</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E9" s="3">
         <v>15000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E10" s="3">
         <v>8500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -871,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,8 +923,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -941,20 +961,23 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D15" s="3">
+        <v>700</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G15" s="3" t="s">
         <v>3</v>
       </c>
@@ -967,8 +990,8 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -976,8 +999,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E17" s="3">
         <v>19800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>41200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,55 +1106,59 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,8 +1180,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1178,43 +1218,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1248,8 +1294,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>2700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,28 +1789,29 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>300</v>
       </c>
       <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>300</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1738,8 +1825,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1773,20 +1863,23 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E43" s="3">
         <v>83100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>71500</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1799,8 +1892,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1808,20 +1901,23 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E44" s="3">
         <v>43100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>47300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1834,8 +1930,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1843,29 +1939,32 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E45" s="3">
         <v>16000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>137700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,29 +1977,32 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>155500</v>
+      </c>
+      <c r="E46" s="3">
         <v>144100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>137400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>139200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>56500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35600</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1913,20 +2015,23 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E47" s="3">
         <v>18600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18400</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,8 +2044,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -1948,20 +2053,23 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E48" s="3">
         <v>32300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33600</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,8 +2082,8 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -1983,8 +2091,11 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1992,14 +2103,14 @@
         <v>61000</v>
       </c>
       <c r="E49" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F49" s="3">
         <v>61700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>60300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,8 +2129,11 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,29 +2205,32 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>51900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19700</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,8 +2243,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,29 +2281,32 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>267300</v>
+      </c>
+      <c r="E54" s="3">
         <v>256000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>251000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>251400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>77300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>55300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,8 +2319,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,20 +2353,21 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E57" s="3">
         <v>52500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48200</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2249,8 +2380,8 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2258,20 +2389,23 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E58" s="3">
         <v>100400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>102700</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,8 +2418,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2293,29 +2427,32 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>155000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>43600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,29 +2465,32 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E60" s="3">
         <v>155600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>153600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>155000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25900</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,29 +2503,32 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>22700</v>
+        <v>22600</v>
       </c>
       <c r="E61" s="3">
         <v>22700</v>
       </c>
       <c r="F61" s="3">
+        <v>22700</v>
+      </c>
+      <c r="G61" s="3">
         <v>10600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2398,29 +2541,32 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E62" s="3">
         <v>17400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2579,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,29 +2693,32 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>235200</v>
+      </c>
+      <c r="E66" s="3">
         <v>225400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>219500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>219700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34600</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2573,8 +2731,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2673,7 +2841,7 @@
         <v>100</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2693,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,29 +2899,32 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E72" s="3">
         <v>7300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,8 +2937,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,29 +3051,32 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E76" s="3">
         <v>30500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20800</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,8 +3089,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,31 +3226,32 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -3063,8 +3262,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>37700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6900</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,23 +3508,24 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-92400</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -3323,8 +3544,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-54500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>11500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3676,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3712,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>22500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-9300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12400</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3653,39 +3902,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ILUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ILUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>ILUS</t>
   </si>
@@ -656,186 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F8" s="3">
         <v>24100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>23500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>19800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>35200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>20400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>19700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2900</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F9" s="3">
         <v>15500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>15000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>13900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>21400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>13600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>13800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F10" s="3">
         <v>8600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>8500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>13800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +875,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,8 +915,14 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +959,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,26 +1003,32 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
       </c>
@@ -993,17 +1038,23 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1066,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="F17" s="3">
         <v>21800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>19800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>17700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>41200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>18500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>18300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F18" s="3">
         <v>2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,64 +1172,72 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>7600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1600</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1183,8 +1256,14 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1221,46 +1300,58 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1388,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1432,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1564,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1608,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1652,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1696,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-7600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1828,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1943,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,35 +1961,37 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1828,31 +2001,37 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1866,26 +2045,32 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>22800</v>
+      </c>
+      <c r="F43" s="3">
         <v>95800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>83100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>71500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1895,35 +2080,41 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F44" s="3">
         <v>39100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>43100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>47300</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1933,44 +2124,50 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F45" s="3">
         <v>18900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>16000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>17200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>137700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>56200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>35300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,35 +2177,41 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>30100</v>
+      </c>
+      <c r="F46" s="3">
         <v>155500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>144100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>137400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>139200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>56500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>35600</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,26 +2221,32 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>18500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>18600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>18400</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2047,35 +2256,41 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>100</v>
+      </c>
+      <c r="F48" s="3">
         <v>32400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>32300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>33600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2085,38 +2300,44 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F49" s="3">
         <v>61000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>61000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>61700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>60300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2132,8 +2353,14 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2397,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,35 +2441,41 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>35100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>51900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>20800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>19700</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,8 +2485,14 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,35 +2529,41 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>62500</v>
+      </c>
+      <c r="F54" s="3">
         <v>267300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>256000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>251000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>251400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>77300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>55300</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2322,8 +2573,14 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2595,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,26 +2613,28 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F57" s="3">
         <v>60000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>52500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>48200</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2383,35 +2644,41 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F58" s="3">
         <v>96700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>100400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>102700</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2421,44 +2688,50 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F59" s="3">
         <v>6100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>155000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>43600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>25900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2468,35 +2741,41 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F60" s="3">
         <v>162900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>155600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>153600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>155000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>43600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>25900</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,35 +2785,41 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F61" s="3">
         <v>22600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>22700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>22700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2544,35 +2829,41 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F62" s="3">
         <v>16400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>17400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>17500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>29700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2582,8 +2873,14 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2917,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2961,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,35 +3005,41 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F66" s="3">
         <v>235200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>225400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>219500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>219700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>54700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>34600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2734,8 +3049,14 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +3071,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +3111,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,13 +3155,19 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>100</v>
@@ -2844,10 +3179,10 @@
         <v>100</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2864,8 +3199,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,35 +3243,41 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F72" s="3">
         <v>7500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>9000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>9700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>22600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>20800</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,8 +3287,14 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3331,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3375,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,35 +3419,41 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F76" s="3">
         <v>32000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>30500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>31500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>31700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>20800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3463,14 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3507,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,20 +3622,22 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3253,11 +3650,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3265,8 +3662,14 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3706,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3750,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3794,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3838,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3882,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>-2000</v>
       </c>
       <c r="E89" s="3">
         <v>1500</v>
       </c>
       <c r="F89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H89" s="3">
         <v>2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>37700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6900</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,26 +3948,28 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-92400</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -3547,8 +3988,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +4032,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +4076,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-54500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>11500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-12000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +4142,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +4182,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +4226,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4270,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4314,58 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>22500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-9300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>12400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4402,54 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>5700</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ILUS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ILUS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
   <si>
     <t>ILUS</t>
   </si>
@@ -656,79 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -736,43 +740,46 @@
         <v>4200</v>
       </c>
       <c r="E8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2900</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,43 +787,46 @@
         <v>2700</v>
       </c>
       <c r="E9" s="3">
+        <v>800</v>
+      </c>
+      <c r="F9" s="3">
         <v>4400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -824,43 +834,46 @@
         <v>1500</v>
       </c>
       <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
         <v>2200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,8 +890,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -921,8 +935,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,8 +982,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1009,29 +1029,32 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1044,8 +1067,8 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1053,8 +1076,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>4600</v>
       </c>
       <c r="E17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F17" s="3">
         <v>12400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,73 +1207,77 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>200</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-300</v>
       </c>
       <c r="E21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-10500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1262,31 +1299,34 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1306,52 +1346,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-500</v>
       </c>
       <c r="E23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1394,8 +1440,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-500</v>
       </c>
       <c r="E26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-700</v>
       </c>
       <c r="E27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
         <v>4800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-700</v>
       </c>
       <c r="E33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-700</v>
       </c>
       <c r="E35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,8 +2049,9 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1972,28 +2059,28 @@
         <v>300</v>
       </c>
       <c r="E41" s="3">
+        <v>300</v>
+      </c>
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>300</v>
       </c>
       <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3">
+        <v>300</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
@@ -2007,17 +2094,20 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,8 +2123,8 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2051,29 +2141,32 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E43" s="3">
         <v>25700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>22800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>95800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>83100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>71500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2086,8 +2179,8 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2095,29 +2188,32 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>39100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>43100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>47300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2130,8 +2226,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2139,38 +2235,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6800</v>
+        <v>7300</v>
       </c>
       <c r="E45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F45" s="3">
         <v>5500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>137700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>56200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,38 +2282,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E46" s="3">
         <v>35200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>144100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>137400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>56500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,29 +2329,32 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>7200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>18500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2262,8 +2367,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2271,29 +2376,32 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33600</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2306,8 +2414,8 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2315,32 +2423,35 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E49" s="3">
         <v>8800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8600</v>
-      </c>
-      <c r="F49" s="3">
-        <v>61000</v>
       </c>
       <c r="G49" s="3">
         <v>61000</v>
       </c>
       <c r="H49" s="3">
+        <v>61000</v>
+      </c>
+      <c r="I49" s="3">
         <v>61700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>60300</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,8 +2470,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,38 +2564,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E52" s="3">
         <v>35100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23600</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>51900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2611,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,38 +2658,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E54" s="3">
         <v>79800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>62500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>267300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>256000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>251000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>251400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>77300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>55300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2705,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,29 +2745,30 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12900</v>
+        <v>4100</v>
       </c>
       <c r="E57" s="3">
-        <v>10100</v>
+        <v>10800</v>
       </c>
       <c r="F57" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G57" s="3">
         <v>60000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>48200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2650,8 +2781,8 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2659,29 +2790,32 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>9300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>96700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>100400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>102700</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,8 +2828,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2703,38 +2837,41 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1300</v>
+        <v>13700</v>
       </c>
       <c r="E59" s="3">
-        <v>2600</v>
+        <v>3300</v>
       </c>
       <c r="F59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G59" s="3">
         <v>6100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>155000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>43600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,38 +2884,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E60" s="3">
         <v>23400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>162900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>155600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>153600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>155000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,38 +2931,41 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E61" s="3">
         <v>13200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>22700</v>
       </c>
       <c r="H61" s="3">
         <v>22700</v>
       </c>
       <c r="I61" s="3">
+        <v>22700</v>
+      </c>
+      <c r="J61" s="3">
         <v>10600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2835,38 +2978,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
         <v>5900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3025,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,38 +3166,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E66" s="3">
         <v>44500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>235200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>225400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>219500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>219700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34600</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3213,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,13 +3326,16 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E70" s="3">
         <v>100</v>
@@ -3185,7 +3353,7 @@
         <v>100</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3205,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,38 +3420,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E72" s="3">
         <v>7700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>22600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20800</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3467,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,38 +3608,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E76" s="3">
         <v>35300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>32000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3655,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-700</v>
       </c>
       <c r="E81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,23 +3822,24 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +3855,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -3668,8 +3867,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>37700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,32 +4170,33 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-92400</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -3994,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,52 +4309,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>11500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4188,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,52 +4563,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E100" s="3">
         <v>10600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>22500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>-9300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4408,48 +4657,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5700</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
